--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126673658</v>
       </c>
       <c r="B3" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>126673347</v>
       </c>
       <c r="B5" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1226,53 +1226,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126670551</v>
+        <v>126673819</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57787</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>205976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
+          <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592453</v>
+        <v>592473</v>
       </c>
       <c r="R7" t="n">
-        <v>6320658</v>
+        <v>6320573</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,9 +1303,19 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,69 +1330,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126673819</v>
+        <v>126670551</v>
       </c>
       <c r="B8" t="n">
-        <v>57787</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592473</v>
+        <v>592453</v>
       </c>
       <c r="R8" t="n">
-        <v>6320573</v>
+        <v>6320658</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,19 +1415,9 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>126670882</v>
       </c>
       <c r="B9" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126670963</v>
       </c>
       <c r="B12" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126673658</v>
       </c>
       <c r="B3" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1003,45 +1003,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126673347</v>
+        <v>126672007</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>58027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592446</v>
+        <v>592555</v>
       </c>
       <c r="R5" t="n">
-        <v>6320506</v>
+        <v>6320562</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1083,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,54 +1119,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126672007</v>
+        <v>126673347</v>
       </c>
       <c r="B6" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592555</v>
+        <v>592446</v>
       </c>
       <c r="R6" t="n">
-        <v>6320562</v>
+        <v>6320506</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1447,7 +1447,7 @@
         <v>126670882</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126670963</v>
       </c>
       <c r="B12" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -1003,54 +1003,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126672007</v>
+        <v>126673347</v>
       </c>
       <c r="B5" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592555</v>
+        <v>592446</v>
       </c>
       <c r="R5" t="n">
-        <v>6320562</v>
+        <v>6320506</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1073,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1083,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,45 +1110,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126673347</v>
+        <v>126672007</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>58027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592446</v>
+        <v>592555</v>
       </c>
       <c r="R6" t="n">
-        <v>6320506</v>
+        <v>6320562</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,57 +1226,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126673819</v>
+        <v>126670551</v>
       </c>
       <c r="B7" t="n">
-        <v>57787</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592473</v>
+        <v>592453</v>
       </c>
       <c r="R7" t="n">
-        <v>6320573</v>
+        <v>6320658</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,19 +1299,9 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,65 +1316,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126670551</v>
+        <v>126673819</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>57787</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>205976</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
+          <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592453</v>
+        <v>592473</v>
       </c>
       <c r="R8" t="n">
-        <v>6320658</v>
+        <v>6320573</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,9 +1405,19 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -1003,45 +1003,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126673347</v>
+        <v>126672007</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>58027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592446</v>
+        <v>592555</v>
       </c>
       <c r="R5" t="n">
-        <v>6320506</v>
+        <v>6320562</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1083,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,54 +1119,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126672007</v>
+        <v>126673347</v>
       </c>
       <c r="B6" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592555</v>
+        <v>592446</v>
       </c>
       <c r="R6" t="n">
-        <v>6320562</v>
+        <v>6320506</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,53 +1226,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126670551</v>
+        <v>126673819</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57787</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>205976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
+          <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592453</v>
+        <v>592473</v>
       </c>
       <c r="R7" t="n">
-        <v>6320658</v>
+        <v>6320573</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,9 +1303,19 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,69 +1330,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126673819</v>
+        <v>126670551</v>
       </c>
       <c r="B8" t="n">
-        <v>57787</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592473</v>
+        <v>592453</v>
       </c>
       <c r="R8" t="n">
-        <v>6320573</v>
+        <v>6320658</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,19 +1415,9 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126673658</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>126673347</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1226,53 +1226,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126670551</v>
+        <v>126673819</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57787</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>205976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
+          <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592453</v>
+        <v>592473</v>
       </c>
       <c r="R7" t="n">
-        <v>6320658</v>
+        <v>6320573</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,9 +1303,19 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,69 +1330,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126673819</v>
+        <v>126670551</v>
       </c>
       <c r="B8" t="n">
-        <v>57787</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592473</v>
+        <v>592453</v>
       </c>
       <c r="R8" t="n">
-        <v>6320573</v>
+        <v>6320658</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,19 +1415,9 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         <v>126670882</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126670963</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>131146362</v>
       </c>
       <c r="B16" t="n">
-        <v>91830</v>
+        <v>91831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>131146362</v>
       </c>
       <c r="B16" t="n">
-        <v>91831</v>
+        <v>91834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>131146362</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -1879,7 +1879,7 @@
         <v>131139047</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>131146326</v>
       </c>
       <c r="B14" t="n">
-        <v>57830</v>
+        <v>57832</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>131146287</v>
       </c>
       <c r="B15" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131146362</v>
       </c>
       <c r="B16" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -1879,7 +1879,7 @@
         <v>131139047</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>131146326</v>
       </c>
       <c r="B14" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>131146287</v>
       </c>
       <c r="B15" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131146362</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -1879,7 +1879,7 @@
         <v>131139047</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>131146326</v>
       </c>
       <c r="B14" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>131146287</v>
       </c>
       <c r="B15" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131146362</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -1879,7 +1879,7 @@
         <v>131139047</v>
       </c>
       <c r="B13" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>131146326</v>
       </c>
       <c r="B14" t="n">
-        <v>57834</v>
+        <v>57837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>131146287</v>
       </c>
       <c r="B15" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131146362</v>
       </c>
       <c r="B16" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -1879,7 +1879,7 @@
         <v>131139047</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>131146326</v>
       </c>
       <c r="B14" t="n">
-        <v>57837</v>
+        <v>57838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>131146287</v>
       </c>
       <c r="B15" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131146362</v>
       </c>
       <c r="B16" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2332,6 +2332,466 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133550712</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Korshamn, Korshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>592511</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6320566</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133549136</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Korshamn, Korshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>592564</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6320559</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133550988</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Korshamn, Korshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>592443</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6320583</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133549202</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57904</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>592634</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6320563</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>133549136</v>
       </c>
       <c r="B18" t="n">
-        <v>91939</v>
+        <v>91941</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>133549136</v>
       </c>
       <c r="B18" t="n">
-        <v>91941</v>
+        <v>91949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79413501</v>
+        <v>126674241</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mönsterås, Sm</t>
+          <t>Ävjevik, Ävjevik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592465.6860433012</v>
+        <v>592514</v>
       </c>
       <c r="R2" t="n">
-        <v>6320684.844322667</v>
+        <v>6320734</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Johansson</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Johansson</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126673658</v>
+        <v>126671035</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,34 +793,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Ersholm, Ersholm, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592447</v>
+        <v>592420</v>
       </c>
       <c r="R3" t="n">
-        <v>6320488</v>
+        <v>6320472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,19 +854,9 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,22 +871,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126670857</v>
+        <v>131146362</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,42 +894,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kälmören, Kälmören, Sm</t>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592529</v>
+        <v>592629</v>
       </c>
       <c r="R4" t="n">
-        <v>6320539</v>
+        <v>6320625</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,28 +969,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126673347</v>
+        <v>133549136</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +999,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,13 +1023,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592446</v>
+        <v>592564</v>
       </c>
       <c r="R5" t="n">
-        <v>6320506</v>
+        <v>6320559</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,22 +1053,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,64 +1088,55 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126672007</v>
+        <v>126670882</v>
       </c>
       <c r="B6" t="n">
-        <v>58027</v>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592555</v>
+        <v>592629</v>
       </c>
       <c r="R6" t="n">
-        <v>6320562</v>
+        <v>6320588</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126670551</v>
+        <v>126670963</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,42 +1213,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
+          <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592453</v>
+        <v>592627</v>
       </c>
       <c r="R7" t="n">
-        <v>6320658</v>
+        <v>6320585</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,9 +1270,19 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,22 +1297,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126673819</v>
+        <v>126673347</v>
       </c>
       <c r="B8" t="n">
-        <v>57787</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1339,46 +1320,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205976</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592473</v>
+        <v>592446</v>
       </c>
       <c r="R8" t="n">
-        <v>6320573</v>
+        <v>6320506</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1379,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1389,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126670882</v>
+        <v>126673658</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,13 +1451,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592629</v>
+        <v>592447</v>
       </c>
       <c r="R9" t="n">
-        <v>6320588</v>
+        <v>6320488</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,7 +1486,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1496,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,14 +1523,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126673835</v>
+        <v>126670551</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1582,7 +1554,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1591,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592527</v>
+        <v>592453</v>
       </c>
       <c r="R10" t="n">
-        <v>6320610</v>
+        <v>6320658</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,27 +1625,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126673363</v>
+        <v>126670857</v>
       </c>
       <c r="B11" t="n">
-        <v>57603</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1681,29 +1653,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Kälmören, Kälmören, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592442</v>
+        <v>592529</v>
       </c>
       <c r="R11" t="n">
-        <v>6320500</v>
+        <v>6320539</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,19 +1698,9 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,60 +1715,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126670963</v>
+        <v>126673614</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Ersholm, Ersholm, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592627</v>
+        <v>592418</v>
       </c>
       <c r="R12" t="n">
-        <v>6320585</v>
+        <v>6320480</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,19 +1800,9 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,26 +1817,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131139047</v>
+        <v>126673835</v>
       </c>
       <c r="B13" t="n">
-        <v>57895</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1904,14 +1857,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1920,13 +1869,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592528</v>
+        <v>592527</v>
       </c>
       <c r="R13" t="n">
-        <v>6320591</v>
+        <v>6320610</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,12 +1899,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,27 +1931,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131146326</v>
+        <v>131139047</v>
       </c>
       <c r="B14" t="n">
-        <v>57844</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2012,34 +1961,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592599</v>
+        <v>592528</v>
       </c>
       <c r="R14" t="n">
-        <v>6320593</v>
+        <v>6320591</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,24 +2008,9 @@
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kom över oss och flög ut mot Gryssholm</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,44 +2025,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131146287</v>
+        <v>126673363</v>
       </c>
       <c r="B15" t="n">
-        <v>58057</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2143,27 +2070,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+          <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592599</v>
+        <v>592442</v>
       </c>
       <c r="R15" t="n">
-        <v>6320593</v>
+        <v>6320500</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2187,22 +2111,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,41 +2153,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131146362</v>
+        <v>131146326</v>
       </c>
       <c r="B16" t="n">
-        <v>91849</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100067</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2271,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592629</v>
+        <v>592599</v>
       </c>
       <c r="R16" t="n">
-        <v>6320625</v>
+        <v>6320593</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2304,18 +2237,32 @@
           <t>2026-02-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kom över oss och flög ut mot Gryssholm</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2334,54 +2281,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550712</v>
+        <v>133549202</v>
       </c>
       <c r="B17" t="n">
-        <v>58461</v>
+        <v>57921</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>100067</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592511</v>
+        <v>592634</v>
       </c>
       <c r="R17" t="n">
-        <v>6320566</v>
+        <v>6320563</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133549136</v>
+        <v>133550988</v>
       </c>
       <c r="B18" t="n">
-        <v>91981</v>
+        <v>58260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,34 +2413,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592564</v>
+        <v>592443</v>
       </c>
       <c r="R18" t="n">
-        <v>6320559</v>
+        <v>6320583</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2550,39 +2511,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133550988</v>
+        <v>79413502</v>
       </c>
       <c r="B19" t="n">
-        <v>58260</v>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2590,21 +2551,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592443</v>
+        <v>592466</v>
       </c>
       <c r="R19" t="n">
-        <v>6320583</v>
+        <v>6320685</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2631,22 +2590,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,39 +2620,39 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Håkan Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Håkan Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133549202</v>
+        <v>126672007</v>
       </c>
       <c r="B20" t="n">
-        <v>57921</v>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100067</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2703,12 +2662,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2718,17 +2672,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+          <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592634</v>
+        <v>592555</v>
       </c>
       <c r="R20" t="n">
-        <v>6320563</v>
+        <v>6320562</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2752,22 +2706,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,6 +2745,471 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133550712</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Korshamn, Korshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>592511</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6320566</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>79413501</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>592466</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6320685</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131146287</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>592599</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6320593</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126673819</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Korshamn, Korshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>592473</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6320573</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34337-2025 artfynd.xlsx
+++ b/artfynd/A 34337-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126674241</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126671035</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131146362</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133549136</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126670882</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126670963</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126673347</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126673658</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126670551</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126670857</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1826,6 +1881,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126673614</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126673835</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2034,6 +2099,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131139047</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2150,6 +2220,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126673363</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2278,6 +2353,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131146326</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2399,6 +2479,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133549202</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2515,6 +2600,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550988</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2629,6 +2719,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79413502</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2745,6 +2840,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126672007</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2861,6 +2961,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550712</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2975,6 +3080,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79413501</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3094,6 +3204,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131146287</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3210,8 +3325,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126673819</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>